--- a/artfynd/A 51955-2023 artfynd.xlsx
+++ b/artfynd/A 51955-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51955-2023 artfynd.xlsx
+++ b/artfynd/A 51955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113888542</v>
+        <v>113886542</v>
       </c>
       <c r="B2" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526707</v>
+        <v>526727</v>
       </c>
       <c r="R2" t="n">
-        <v>6910080</v>
+        <v>6909885</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113888544</v>
+        <v>113886544</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526811</v>
+        <v>526593</v>
       </c>
       <c r="R3" t="n">
-        <v>6910150</v>
+        <v>6910144</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113887072</v>
+        <v>113888532</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526652</v>
+        <v>526606</v>
       </c>
       <c r="R4" t="n">
-        <v>6909857</v>
+        <v>6909900</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113888532</v>
+        <v>113888542</v>
       </c>
       <c r="B5" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526606</v>
+        <v>526707</v>
       </c>
       <c r="R5" t="n">
-        <v>6909900</v>
+        <v>6910080</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113886790</v>
+        <v>113888543</v>
       </c>
       <c r="B6" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526652</v>
+        <v>526842</v>
       </c>
       <c r="R6" t="n">
-        <v>6909857</v>
+        <v>6910380</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1233,16 +1208,11 @@
         <v>113887760</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113888044</v>
+        <v>113887761</v>
       </c>
       <c r="B8" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526607</v>
+        <v>526734</v>
       </c>
       <c r="R8" t="n">
-        <v>6910150</v>
+        <v>6910080</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113887761</v>
+        <v>113888541</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526734</v>
+        <v>526611</v>
       </c>
       <c r="R9" t="n">
-        <v>6910080</v>
+        <v>6910350</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113888543</v>
+        <v>113888044</v>
       </c>
       <c r="B10" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526842</v>
+        <v>526607</v>
       </c>
       <c r="R10" t="n">
-        <v>6910380</v>
+        <v>6910150</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113886544</v>
+        <v>113888544</v>
       </c>
       <c r="B11" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526593</v>
+        <v>526811</v>
       </c>
       <c r="R11" t="n">
-        <v>6910144</v>
+        <v>6910150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,37 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113886542</v>
+        <v>113886790</v>
       </c>
       <c r="B12" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526727</v>
+        <v>526652</v>
       </c>
       <c r="R12" t="n">
-        <v>6909885</v>
+        <v>6909857</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1893,6 +1838,112 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113887072</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nylandet, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>526652</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6909857</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51955-2023 artfynd.xlsx
+++ b/artfynd/A 51955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888532</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888543</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887760</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887761</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888044</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888544</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886790</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,8 +2004,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>